--- a/papers.xlsx
+++ b/papers.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/f35f2ade6f83fb43/Neuroscience Center/OT-Explorer/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="2" documentId="11_AD4D066CA252ABDACC1048DF6110DAE672EEDF51" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{B831E630-2DD5-4569-87E5-B933B1569206}"/>
+  <xr:revisionPtr revIDLastSave="22" documentId="11_AD4D066CA252ABDACC1048DF6110DAE672EEDF51" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{FAD2CA98-2E81-4B7B-9E44-E5987BCAC4A9}"/>
   <bookViews>
-    <workbookView xWindow="-13620" yWindow="-120" windowWidth="13740" windowHeight="23640" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="1056" yWindow="-108" windowWidth="22092" windowHeight="13176" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="28" uniqueCount="28">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="17" uniqueCount="17">
   <si>
     <t>title</t>
   </si>
@@ -57,58 +57,30 @@
     <t>summary</t>
   </si>
   <si>
-    <t>Transcriptomic mapping of the 5-HT receptor landscape</t>
-  </si>
-  <si>
-    <t>De Filippo et al.</t>
-  </si>
-  <si>
-    <t>Patterns</t>
-  </si>
-  <si>
-    <t>Atlas</t>
-  </si>
-  <si>
-    <t>Mouse</t>
-  </si>
-  <si>
-    <t>MERFISH</t>
-  </si>
-  <si>
-    <t>5HT,receptor,atlas</t>
-  </si>
-  <si>
-    <t>https://www.cell.com/patterns/fulltext/S2666-3899(24)00173-5</t>
-  </si>
-  <si>
-    <t>Whole-brain serotonin receptor atlas.</t>
-  </si>
-  <si>
-    <t>Mu opioid hedonic hotspot in olfactory tubercle</t>
-  </si>
-  <si>
-    <t>Castro and Berridge</t>
-  </si>
-  <si>
-    <t>PNAS</t>
+    <t>Microinjection</t>
+  </si>
+  <si>
+    <t>Hedonic hotspot in rat olfactory tubercle: map for mu-opioid, orexin, and muscimol enhancement of sucrose 'liking'</t>
+  </si>
+  <si>
+    <t>Koshi Murata &amp; Kent C Berriddge</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>NPP</t>
+    <phoneticPr fontId="1"/>
   </si>
   <si>
     <t>Behavior</t>
+    <phoneticPr fontId="1"/>
   </si>
   <si>
     <t>Rat</t>
-  </si>
-  <si>
-    <t>Microinjection</t>
-  </si>
-  <si>
-    <t>opioid,hedonic hotspot</t>
-  </si>
-  <si>
-    <t>https://www.pnas.org/doi/10.1073/pnas.1423442112</t>
-  </si>
-  <si>
-    <t>Hedonic hotspot in OT medial shell.</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>opioid,orexin,hotspot</t>
+    <phoneticPr fontId="1"/>
   </si>
 </sst>
 </file>
@@ -168,6 +140,10 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -433,8 +409,14 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:J3"/>
+  <dimension ref="A1:J2"/>
   <sheetFormatPr defaultRowHeight="18"/>
+  <cols>
+    <col min="1" max="1" width="50.69921875" customWidth="1"/>
+    <col min="2" max="2" width="27.796875" customWidth="1"/>
+    <col min="3" max="3" width="10.3984375" customWidth="1"/>
+    <col min="5" max="5" width="11.5" customWidth="1"/>
+  </cols>
   <sheetData>
     <row r="1" spans="1:10">
       <c r="A1" t="s">
@@ -470,70 +452,33 @@
     </row>
     <row r="2" spans="1:10">
       <c r="A2" t="s">
+        <v>11</v>
+      </c>
+      <c r="B2" t="s">
+        <v>12</v>
+      </c>
+      <c r="C2" t="s">
+        <v>13</v>
+      </c>
+      <c r="D2">
+        <v>2026</v>
+      </c>
+      <c r="E2" t="s">
+        <v>14</v>
+      </c>
+      <c r="F2" t="s">
+        <v>15</v>
+      </c>
+      <c r="G2" t="s">
         <v>10</v>
-      </c>
-      <c r="B2" t="s">
-        <v>11</v>
-      </c>
-      <c r="C2" t="s">
-        <v>12</v>
-      </c>
-      <c r="D2">
-        <v>2024</v>
-      </c>
-      <c r="E2" t="s">
-        <v>13</v>
-      </c>
-      <c r="F2" t="s">
-        <v>14</v>
-      </c>
-      <c r="G2" t="s">
-        <v>15</v>
       </c>
       <c r="H2" t="s">
         <v>16</v>
-      </c>
-      <c r="I2" t="s">
-        <v>17</v>
-      </c>
-      <c r="J2" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="3" spans="1:10">
-      <c r="A3" t="s">
-        <v>19</v>
-      </c>
-      <c r="B3" t="s">
-        <v>20</v>
-      </c>
-      <c r="C3" t="s">
-        <v>21</v>
-      </c>
-      <c r="D3">
-        <v>2015</v>
-      </c>
-      <c r="E3" t="s">
-        <v>22</v>
-      </c>
-      <c r="F3" t="s">
-        <v>23</v>
-      </c>
-      <c r="G3" t="s">
-        <v>24</v>
-      </c>
-      <c r="H3" t="s">
-        <v>25</v>
-      </c>
-      <c r="I3" t="s">
-        <v>26</v>
-      </c>
-      <c r="J3" t="s">
-        <v>27</v>
       </c>
     </row>
   </sheetData>
   <phoneticPr fontId="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="0" verticalDpi="0" r:id="rId1"/>
 </worksheet>
 </file>
--- a/papers.xlsx
+++ b/papers.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/f35f2ade6f83fb43/Neuroscience Center/OT-Explorer/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="22" documentId="11_AD4D066CA252ABDACC1048DF6110DAE672EEDF51" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{FAD2CA98-2E81-4B7B-9E44-E5987BCAC4A9}"/>
+  <xr:revisionPtr revIDLastSave="23" documentId="11_AD4D066CA252ABDACC1048DF6110DAE672EEDF51" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{A14C393F-E9C7-43BB-A333-0D8220DCB722}"/>
   <bookViews>
     <workbookView xWindow="1056" yWindow="-108" windowWidth="22092" windowHeight="13176" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="17" uniqueCount="17">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="18" uniqueCount="18">
   <si>
     <t>title</t>
   </si>
@@ -80,6 +80,10 @@
   </si>
   <si>
     <t>opioid,orexin,hotspot</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>https://www.nature.com/articles/s41386-026-02374-6</t>
     <phoneticPr fontId="1"/>
   </si>
 </sst>
@@ -87,7 +91,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2">
+  <fonts count="3">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -100,6 +104,14 @@
       <name val="Yu Gothic"/>
       <family val="3"/>
       <charset val="128"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color theme="10"/>
+      <name val="Yu Gothic"/>
+      <family val="2"/>
       <scheme val="minor"/>
     </font>
   </fonts>
@@ -120,13 +132,16 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1"/>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="2">
+    <cellStyle name="ハイパーリンク" xfId="1" builtinId="8"/>
     <cellStyle name="標準" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
@@ -475,10 +490,16 @@
       <c r="H2" t="s">
         <v>16</v>
       </c>
+      <c r="I2" s="1" t="s">
+        <v>17</v>
+      </c>
     </row>
   </sheetData>
   <phoneticPr fontId="1"/>
+  <hyperlinks>
+    <hyperlink ref="I2" r:id="rId1" xr:uid="{2CEAE1B4-C22E-41A8-8A1A-9EEB08AD56EB}"/>
+  </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="0" verticalDpi="0" r:id="rId1"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="0" verticalDpi="0" r:id="rId2"/>
 </worksheet>
 </file>
--- a/papers.xlsx
+++ b/papers.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/f35f2ade6f83fb43/Neuroscience Center/OT-Explorer/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="23" documentId="11_AD4D066CA252ABDACC1048DF6110DAE672EEDF51" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{A14C393F-E9C7-43BB-A333-0D8220DCB722}"/>
+  <xr:revisionPtr revIDLastSave="27" documentId="11_AD4D066CA252ABDACC1048DF6110DAE672EEDF51" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{ABF6645B-B04A-4638-B8F5-640848766D03}"/>
   <bookViews>
     <workbookView xWindow="1056" yWindow="-108" windowWidth="22092" windowHeight="13176" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="18" uniqueCount="18">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="13" uniqueCount="13">
   <si>
     <t>title</t>
   </si>
@@ -42,22 +42,10 @@
     <t>category</t>
   </si>
   <si>
-    <t>species</t>
-  </si>
-  <si>
-    <t>method</t>
-  </si>
-  <si>
     <t>tags</t>
   </si>
   <si>
     <t>url</t>
-  </si>
-  <si>
-    <t>summary</t>
-  </si>
-  <si>
-    <t>Microinjection</t>
   </si>
   <si>
     <t>Hedonic hotspot in rat olfactory tubercle: map for mu-opioid, orexin, and muscimol enhancement of sucrose 'liking'</t>
@@ -67,23 +55,19 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>NPP</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
     <t>Behavior</t>
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>Rat</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
     <t>opioid,orexin,hotspot</t>
     <phoneticPr fontId="1"/>
   </si>
   <si>
     <t>https://www.nature.com/articles/s41386-026-02374-6</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>Neuropsychopharmacology</t>
     <phoneticPr fontId="1"/>
   </si>
 </sst>
@@ -424,7 +408,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:J2"/>
+  <dimension ref="A1:G2"/>
   <sheetFormatPr defaultRowHeight="18"/>
   <cols>
     <col min="1" max="1" width="50.69921875" customWidth="1"/>
@@ -433,7 +417,7 @@
     <col min="5" max="5" width="11.5" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10">
+    <row r="1" spans="1:7">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -455,49 +439,34 @@
       <c r="G1" t="s">
         <v>6</v>
       </c>
-      <c r="H1" t="s">
+    </row>
+    <row r="2" spans="1:7">
+      <c r="A2" t="s">
         <v>7</v>
       </c>
-      <c r="I1" t="s">
+      <c r="B2" t="s">
         <v>8</v>
       </c>
-      <c r="J1" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="2" spans="1:10">
-      <c r="A2" t="s">
-        <v>11</v>
-      </c>
-      <c r="B2" t="s">
+      <c r="C2" t="s">
         <v>12</v>
-      </c>
-      <c r="C2" t="s">
-        <v>13</v>
       </c>
       <c r="D2">
         <v>2026</v>
       </c>
       <c r="E2" t="s">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="F2" t="s">
-        <v>15</v>
-      </c>
-      <c r="G2" t="s">
         <v>10</v>
       </c>
-      <c r="H2" t="s">
-        <v>16</v>
-      </c>
-      <c r="I2" s="1" t="s">
-        <v>17</v>
+      <c r="G2" s="1" t="s">
+        <v>11</v>
       </c>
     </row>
   </sheetData>
   <phoneticPr fontId="1"/>
   <hyperlinks>
-    <hyperlink ref="I2" r:id="rId1" xr:uid="{2CEAE1B4-C22E-41A8-8A1A-9EEB08AD56EB}"/>
+    <hyperlink ref="G2" r:id="rId1" xr:uid="{2CEAE1B4-C22E-41A8-8A1A-9EEB08AD56EB}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="0" verticalDpi="0" r:id="rId2"/>

--- a/papers.xlsx
+++ b/papers.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/f35f2ade6f83fb43/Neuroscience Center/OT-Explorer/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="27" documentId="11_AD4D066CA252ABDACC1048DF6110DAE672EEDF51" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{ABF6645B-B04A-4638-B8F5-640848766D03}"/>
+  <xr:revisionPtr revIDLastSave="58" documentId="11_AD4D066CA252ABDACC1048DF6110DAE672EEDF51" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{F8A7618B-5B63-48D5-89F9-BB2756CADA7C}"/>
   <bookViews>
     <workbookView xWindow="1056" yWindow="-108" windowWidth="22092" windowHeight="13176" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="13" uniqueCount="13">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="37" uniqueCount="30">
   <si>
     <t>title</t>
   </si>
@@ -55,10 +55,6 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>Behavior</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
     <t>opioid,orexin,hotspot</t>
     <phoneticPr fontId="1"/>
   </si>
@@ -68,6 +64,76 @@
   </si>
   <si>
     <t>Neuropsychopharmacology</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>Endogenous opioids in the olfactory tubercle and their roles in olfaction and quality of life</t>
+  </si>
+  <si>
+    <t>Koshi Murata et al.</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>Pharmacology</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>Neurochemistry</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>opioid,Dynprphin,Enkephalin</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>Front Neural Circuits.</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>https://www.frontiersin.org/journals/neural-circuits/articles/10.3389/fncir.2024.1408189/full</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>Cellular Profiles of Prodynorphin and Preproenkephalin mRNA-Expressing Neurons in the Anterior Olfactory Tubercle of Mice</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>https://www.frontiersin.org/journals/neural-circuits/articles/10.3389/fncir.2022.908964/full</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>Review</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>attractive, aversive, eating, motivation</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>Hypothetical Roles of the Olfactory Tubercle in Odor-Guided Eating Behavior</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>GABAergic neurons in the olfactory cortex projecting to the lateral hypothalamus in mice</t>
+  </si>
+  <si>
+    <t>Scientific Reports</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>Anatomy</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>hypothalamus, feeding</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>https://www.nature.com/articles/s41598-019-43580-1</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>https://www.frontiersin.org/journals/neural-circuits/articles/10.3389/fncir.2020.577880/full</t>
     <phoneticPr fontId="1"/>
   </si>
 </sst>
@@ -408,10 +474,10 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:G2"/>
+  <dimension ref="A1:G6"/>
   <sheetFormatPr defaultRowHeight="18"/>
   <cols>
-    <col min="1" max="1" width="50.69921875" customWidth="1"/>
+    <col min="1" max="1" width="61.19921875" customWidth="1"/>
     <col min="2" max="2" width="27.796875" customWidth="1"/>
     <col min="3" max="3" width="10.3984375" customWidth="1"/>
     <col min="5" max="5" width="11.5" customWidth="1"/>
@@ -448,27 +514,123 @@
         <v>8</v>
       </c>
       <c r="C2" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="D2">
         <v>2026</v>
       </c>
       <c r="E2" t="s">
+        <v>14</v>
+      </c>
+      <c r="F2" t="s">
         <v>9</v>
       </c>
-      <c r="F2" t="s">
+      <c r="G2" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="G2" s="1" t="s">
-        <v>11</v>
+    </row>
+    <row r="3" spans="1:7">
+      <c r="A3" t="s">
+        <v>12</v>
+      </c>
+      <c r="B3" t="s">
+        <v>13</v>
+      </c>
+      <c r="C3" t="s">
+        <v>17</v>
+      </c>
+      <c r="D3">
+        <v>2024</v>
+      </c>
+      <c r="E3" t="s">
+        <v>15</v>
+      </c>
+      <c r="F3" t="s">
+        <v>16</v>
+      </c>
+      <c r="G3" s="1" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7">
+      <c r="A4" t="s">
+        <v>19</v>
+      </c>
+      <c r="B4" t="s">
+        <v>13</v>
+      </c>
+      <c r="C4" t="s">
+        <v>17</v>
+      </c>
+      <c r="D4">
+        <v>2022</v>
+      </c>
+      <c r="E4" t="s">
+        <v>15</v>
+      </c>
+      <c r="F4" t="s">
+        <v>16</v>
+      </c>
+      <c r="G4" s="1" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7">
+      <c r="A5" t="s">
+        <v>23</v>
+      </c>
+      <c r="B5" t="s">
+        <v>13</v>
+      </c>
+      <c r="C5" t="s">
+        <v>17</v>
+      </c>
+      <c r="D5">
+        <v>2020</v>
+      </c>
+      <c r="E5" t="s">
+        <v>21</v>
+      </c>
+      <c r="F5" t="s">
+        <v>22</v>
+      </c>
+      <c r="G5" s="1" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7">
+      <c r="A6" t="s">
+        <v>24</v>
+      </c>
+      <c r="B6" t="s">
+        <v>13</v>
+      </c>
+      <c r="C6" t="s">
+        <v>25</v>
+      </c>
+      <c r="D6">
+        <v>2019</v>
+      </c>
+      <c r="E6" t="s">
+        <v>26</v>
+      </c>
+      <c r="F6" t="s">
+        <v>27</v>
+      </c>
+      <c r="G6" s="1" t="s">
+        <v>28</v>
       </c>
     </row>
   </sheetData>
   <phoneticPr fontId="1"/>
   <hyperlinks>
     <hyperlink ref="G2" r:id="rId1" xr:uid="{2CEAE1B4-C22E-41A8-8A1A-9EEB08AD56EB}"/>
+    <hyperlink ref="G3" r:id="rId2" xr:uid="{06FCE9FD-C4D8-4756-9A94-806CCD0B84E3}"/>
+    <hyperlink ref="G4" r:id="rId3" xr:uid="{83E9E08B-47C9-4835-BD1E-0DF9920B2026}"/>
+    <hyperlink ref="G6" r:id="rId4" xr:uid="{FBB6245B-B4D4-4244-AC31-55CA3D01B295}"/>
+    <hyperlink ref="G5" r:id="rId5" xr:uid="{91B70FAC-CC1D-447E-BE91-98199374223B}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="0" verticalDpi="0" r:id="rId2"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="0" verticalDpi="0" r:id="rId6"/>
 </worksheet>
 </file>
--- a/papers.xlsx
+++ b/papers.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/f35f2ade6f83fb43/Neuroscience Center/OT-Explorer/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="58" documentId="11_AD4D066CA252ABDACC1048DF6110DAE672EEDF51" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{F8A7618B-5B63-48D5-89F9-BB2756CADA7C}"/>
+  <xr:revisionPtr revIDLastSave="60" documentId="11_AD4D066CA252ABDACC1048DF6110DAE672EEDF51" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{E1C0699F-7EA9-488F-8589-15E88D6AB651}"/>
   <bookViews>
     <workbookView xWindow="1056" yWindow="-108" windowWidth="22092" windowHeight="13176" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,71 +25,27 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="37" uniqueCount="30">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="13" uniqueCount="13">
   <si>
     <t>title</t>
   </si>
   <si>
-    <t>authors</t>
-  </si>
-  <si>
-    <t>journal</t>
-  </si>
-  <si>
     <t>year</t>
   </si>
   <si>
-    <t>category</t>
-  </si>
-  <si>
-    <t>tags</t>
-  </si>
-  <si>
     <t>url</t>
   </si>
   <si>
     <t>Hedonic hotspot in rat olfactory tubercle: map for mu-opioid, orexin, and muscimol enhancement of sucrose 'liking'</t>
   </si>
   <si>
-    <t>Koshi Murata &amp; Kent C Berriddge</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>opioid,orexin,hotspot</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
     <t>https://www.nature.com/articles/s41386-026-02374-6</t>
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>Neuropsychopharmacology</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
     <t>Endogenous opioids in the olfactory tubercle and their roles in olfaction and quality of life</t>
   </si>
   <si>
-    <t>Koshi Murata et al.</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>Pharmacology</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>Neurochemistry</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>opioid,Dynprphin,Enkephalin</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>Front Neural Circuits.</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
     <t>https://www.frontiersin.org/journals/neural-circuits/articles/10.3389/fncir.2024.1408189/full</t>
     <phoneticPr fontId="1"/>
   </si>
@@ -102,31 +58,11 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>Review</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>attractive, aversive, eating, motivation</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
     <t>Hypothetical Roles of the Olfactory Tubercle in Odor-Guided Eating Behavior</t>
     <phoneticPr fontId="1"/>
   </si>
   <si>
     <t>GABAergic neurons in the olfactory cortex projecting to the lateral hypothalamus in mice</t>
-  </si>
-  <si>
-    <t>Scientific Reports</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>Anatomy</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>hypothalamus, feeding</t>
-    <phoneticPr fontId="1"/>
   </si>
   <si>
     <t>https://www.nature.com/articles/s41598-019-43580-1</t>
@@ -474,16 +410,13 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:G6"/>
+  <dimension ref="A1:C6"/>
   <sheetFormatPr defaultRowHeight="18"/>
   <cols>
     <col min="1" max="1" width="61.19921875" customWidth="1"/>
-    <col min="2" max="2" width="27.796875" customWidth="1"/>
-    <col min="3" max="3" width="10.3984375" customWidth="1"/>
-    <col min="5" max="5" width="11.5" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7">
+    <row r="1" spans="1:3">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -493,142 +426,70 @@
       <c r="C1" t="s">
         <v>2</v>
       </c>
-      <c r="D1" t="s">
+    </row>
+    <row r="2" spans="1:3">
+      <c r="A2" t="s">
         <v>3</v>
       </c>
-      <c r="E1" t="s">
+      <c r="B2">
+        <v>2026</v>
+      </c>
+      <c r="C2" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="F1" t="s">
+    </row>
+    <row r="3" spans="1:3">
+      <c r="A3" t="s">
         <v>5</v>
       </c>
-      <c r="G1" t="s">
+      <c r="B3">
+        <v>2024</v>
+      </c>
+      <c r="C3" s="1" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="2" spans="1:7">
-      <c r="A2" t="s">
+    <row r="4" spans="1:3">
+      <c r="A4" t="s">
         <v>7</v>
       </c>
-      <c r="B2" t="s">
+      <c r="B4">
+        <v>2022</v>
+      </c>
+      <c r="C4" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="C2" t="s">
+    </row>
+    <row r="5" spans="1:3">
+      <c r="A5" t="s">
+        <v>9</v>
+      </c>
+      <c r="B5">
+        <v>2020</v>
+      </c>
+      <c r="C5" s="1" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3">
+      <c r="A6" t="s">
+        <v>10</v>
+      </c>
+      <c r="B6">
+        <v>2019</v>
+      </c>
+      <c r="C6" s="1" t="s">
         <v>11</v>
-      </c>
-      <c r="D2">
-        <v>2026</v>
-      </c>
-      <c r="E2" t="s">
-        <v>14</v>
-      </c>
-      <c r="F2" t="s">
-        <v>9</v>
-      </c>
-      <c r="G2" s="1" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="3" spans="1:7">
-      <c r="A3" t="s">
-        <v>12</v>
-      </c>
-      <c r="B3" t="s">
-        <v>13</v>
-      </c>
-      <c r="C3" t="s">
-        <v>17</v>
-      </c>
-      <c r="D3">
-        <v>2024</v>
-      </c>
-      <c r="E3" t="s">
-        <v>15</v>
-      </c>
-      <c r="F3" t="s">
-        <v>16</v>
-      </c>
-      <c r="G3" s="1" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="4" spans="1:7">
-      <c r="A4" t="s">
-        <v>19</v>
-      </c>
-      <c r="B4" t="s">
-        <v>13</v>
-      </c>
-      <c r="C4" t="s">
-        <v>17</v>
-      </c>
-      <c r="D4">
-        <v>2022</v>
-      </c>
-      <c r="E4" t="s">
-        <v>15</v>
-      </c>
-      <c r="F4" t="s">
-        <v>16</v>
-      </c>
-      <c r="G4" s="1" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="5" spans="1:7">
-      <c r="A5" t="s">
-        <v>23</v>
-      </c>
-      <c r="B5" t="s">
-        <v>13</v>
-      </c>
-      <c r="C5" t="s">
-        <v>17</v>
-      </c>
-      <c r="D5">
-        <v>2020</v>
-      </c>
-      <c r="E5" t="s">
-        <v>21</v>
-      </c>
-      <c r="F5" t="s">
-        <v>22</v>
-      </c>
-      <c r="G5" s="1" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="6" spans="1:7">
-      <c r="A6" t="s">
-        <v>24</v>
-      </c>
-      <c r="B6" t="s">
-        <v>13</v>
-      </c>
-      <c r="C6" t="s">
-        <v>25</v>
-      </c>
-      <c r="D6">
-        <v>2019</v>
-      </c>
-      <c r="E6" t="s">
-        <v>26</v>
-      </c>
-      <c r="F6" t="s">
-        <v>27</v>
-      </c>
-      <c r="G6" s="1" t="s">
-        <v>28</v>
       </c>
     </row>
   </sheetData>
   <phoneticPr fontId="1"/>
   <hyperlinks>
-    <hyperlink ref="G2" r:id="rId1" xr:uid="{2CEAE1B4-C22E-41A8-8A1A-9EEB08AD56EB}"/>
-    <hyperlink ref="G3" r:id="rId2" xr:uid="{06FCE9FD-C4D8-4756-9A94-806CCD0B84E3}"/>
-    <hyperlink ref="G4" r:id="rId3" xr:uid="{83E9E08B-47C9-4835-BD1E-0DF9920B2026}"/>
-    <hyperlink ref="G6" r:id="rId4" xr:uid="{FBB6245B-B4D4-4244-AC31-55CA3D01B295}"/>
-    <hyperlink ref="G5" r:id="rId5" xr:uid="{91B70FAC-CC1D-447E-BE91-98199374223B}"/>
+    <hyperlink ref="C2" r:id="rId1" xr:uid="{2CEAE1B4-C22E-41A8-8A1A-9EEB08AD56EB}"/>
+    <hyperlink ref="C3" r:id="rId2" xr:uid="{06FCE9FD-C4D8-4756-9A94-806CCD0B84E3}"/>
+    <hyperlink ref="C4" r:id="rId3" xr:uid="{83E9E08B-47C9-4835-BD1E-0DF9920B2026}"/>
+    <hyperlink ref="C6" r:id="rId4" xr:uid="{FBB6245B-B4D4-4244-AC31-55CA3D01B295}"/>
+    <hyperlink ref="C5" r:id="rId5" xr:uid="{91B70FAC-CC1D-447E-BE91-98199374223B}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="0" verticalDpi="0" r:id="rId6"/>

--- a/papers.xlsx
+++ b/papers.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/f35f2ade6f83fb43/Neuroscience Center/OT-Explorer/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="60" documentId="11_AD4D066CA252ABDACC1048DF6110DAE672EEDF51" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{E1C0699F-7EA9-488F-8589-15E88D6AB651}"/>
+  <xr:revisionPtr revIDLastSave="103" documentId="11_AD4D066CA252ABDACC1048DF6110DAE672EEDF51" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{7A8364E7-04E4-4B78-9057-73135026A972}"/>
   <bookViews>
     <workbookView xWindow="1056" yWindow="-108" windowWidth="22092" windowHeight="13176" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="13" uniqueCount="13">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="35" uniqueCount="35">
   <si>
     <t>title</t>
   </si>
@@ -70,6 +70,84 @@
   </si>
   <si>
     <t>https://www.frontiersin.org/journals/neural-circuits/articles/10.3389/fncir.2020.577880/full</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>Mapping of Learned Odor-Induced Motivated Behaviors in the Mouse Olfactory Tubercle</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>https://www.jneurosci.org/content/35/29/10581.long</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>Differential potentiation of odor aversion and yawning by melanocortin 4 receptor signaling in distinct regions of the ventral striatum</t>
+  </si>
+  <si>
+    <t>https://www.frontiersin.org/journals/neuroscience/articles/10.3389/fnins.2025.1668410/full</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>Function of orexin-1 receptor signaling in the olfactory tubercle in odor-guided attraction and aversion</t>
+  </si>
+  <si>
+    <t>https://www.nature.com/articles/s42003-024-07438-1</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>Synaptic plasticity and roles of orexin in distinct domains of the olfactory tubercle</t>
+  </si>
+  <si>
+    <t>https://www.frontiersin.org/journals/neural-circuits/articles/10.3389/fncir.2024.1473403/full</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>Learning-dependent structural plasticity of intracortical and sensory connections to functional domains of the olfactory tubercle</t>
+  </si>
+  <si>
+    <t>https://www.frontiersin.org/journals/neuroscience/articles/10.3389/fnins.2023.1247375/full</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>Expression of feeding-related neuromodulatory signalling molecules in the mouse central olfactory system</t>
+  </si>
+  <si>
+    <t>https://www.nature.com/articles/s41598-020-57605-7</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>Opposing Roles of Dopamine Receptor D1- and D2-Expressing Neurons in the Anteromedial Olfactory Tubercle in Acquisition of Place Preference in Mice</t>
+  </si>
+  <si>
+    <t>https://www.frontiersin.org/journals/behavioral-neuroscience/articles/10.3389/fnbeh.2019.00050/full</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>https://www.nature.com/articles/s41598-018-31604-1</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>Functional development of olfactory tubercle domains during weaning period in mice</t>
+  </si>
+  <si>
+    <t>Functional Sub-Circuits of the Olfactory System Viewed from the Olfactory Bulb and the Olfactory Tubercle</t>
+  </si>
+  <si>
+    <t>https://www.frontiersin.org/journals/neuroanatomy/articles/10.3389/fnana.2017.00033/full</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>Feeding-induced olfactory cortex suppression reduces satiation</t>
+  </si>
+  <si>
+    <t>https://www.cell.com/neuron/fulltext/S0896-6273(25)00547-1?_returnURL=https%3A%2F%2Flinkinghub.elsevier.com%2Fretrieve%2Fpii%2FS0896627325005471%3Fshowall%3Dtrue</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>Distinct representation of cue-outcome association by D1 and D2 neurons in the ventral striatum’s olfactory tubercle</t>
+  </si>
+  <si>
+    <t>https://elifesciences.org/articles/75463</t>
     <phoneticPr fontId="1"/>
   </si>
 </sst>
@@ -410,10 +488,10 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:C6"/>
+  <dimension ref="A1:C17"/>
   <sheetFormatPr defaultRowHeight="18"/>
   <cols>
-    <col min="1" max="1" width="61.19921875" customWidth="1"/>
+    <col min="1" max="1" width="79" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3">
@@ -480,6 +558,127 @@
       </c>
       <c r="C6" s="1" t="s">
         <v>11</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3">
+      <c r="A7" t="s">
+        <v>13</v>
+      </c>
+      <c r="B7">
+        <v>2015</v>
+      </c>
+      <c r="C7" s="1" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3">
+      <c r="A8" t="s">
+        <v>15</v>
+      </c>
+      <c r="B8">
+        <v>2025</v>
+      </c>
+      <c r="C8" s="1" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3">
+      <c r="A9" t="s">
+        <v>17</v>
+      </c>
+      <c r="B9">
+        <v>2024</v>
+      </c>
+      <c r="C9" s="1" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3">
+      <c r="A10" t="s">
+        <v>19</v>
+      </c>
+      <c r="B10">
+        <v>2024</v>
+      </c>
+      <c r="C10" s="1" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="11" spans="1:3">
+      <c r="A11" t="s">
+        <v>21</v>
+      </c>
+      <c r="B11">
+        <v>2023</v>
+      </c>
+      <c r="C11" s="1" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="12" spans="1:3">
+      <c r="A12" t="s">
+        <v>23</v>
+      </c>
+      <c r="B12">
+        <v>2020</v>
+      </c>
+      <c r="C12" s="1" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="13" spans="1:3">
+      <c r="A13" t="s">
+        <v>25</v>
+      </c>
+      <c r="B13">
+        <v>2019</v>
+      </c>
+      <c r="C13" s="1" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="14" spans="1:3">
+      <c r="A14" t="s">
+        <v>28</v>
+      </c>
+      <c r="B14">
+        <v>2018</v>
+      </c>
+      <c r="C14" s="1" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="15" spans="1:3">
+      <c r="A15" t="s">
+        <v>29</v>
+      </c>
+      <c r="B15">
+        <v>2017</v>
+      </c>
+      <c r="C15" s="1" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="16" spans="1:3">
+      <c r="A16" t="s">
+        <v>31</v>
+      </c>
+      <c r="B16">
+        <v>2025</v>
+      </c>
+      <c r="C16" s="1" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="17" spans="1:3">
+      <c r="A17" t="s">
+        <v>33</v>
+      </c>
+      <c r="B17">
+        <v>2022</v>
+      </c>
+      <c r="C17" s="1" t="s">
+        <v>34</v>
       </c>
     </row>
   </sheetData>
@@ -490,8 +689,19 @@
     <hyperlink ref="C4" r:id="rId3" xr:uid="{83E9E08B-47C9-4835-BD1E-0DF9920B2026}"/>
     <hyperlink ref="C6" r:id="rId4" xr:uid="{FBB6245B-B4D4-4244-AC31-55CA3D01B295}"/>
     <hyperlink ref="C5" r:id="rId5" xr:uid="{91B70FAC-CC1D-447E-BE91-98199374223B}"/>
+    <hyperlink ref="C7" r:id="rId6" xr:uid="{87E61370-AF2B-4826-A973-5B3AC8EA20A5}"/>
+    <hyperlink ref="C8" r:id="rId7" xr:uid="{DE3E7C1B-598F-4BBC-AE2D-CC49EA52FB55}"/>
+    <hyperlink ref="C9" r:id="rId8" xr:uid="{CFD3C4B4-3884-443F-9587-C39A88C2C016}"/>
+    <hyperlink ref="C10" r:id="rId9" xr:uid="{AE8BE3A5-2DC6-4B05-9008-62A5CFE60707}"/>
+    <hyperlink ref="C11" r:id="rId10" xr:uid="{990E9D21-BCA1-4523-AA0E-D13FB8E97A48}"/>
+    <hyperlink ref="C12" r:id="rId11" xr:uid="{8A4B0AA9-98B2-4381-A779-D19DFF8BCBFE}"/>
+    <hyperlink ref="C13" r:id="rId12" xr:uid="{0C39EADF-6B34-49BD-A9F5-4DBE16B021EF}"/>
+    <hyperlink ref="C14" r:id="rId13" xr:uid="{17D6A5D0-7F9E-45F7-BBEE-374D226391B4}"/>
+    <hyperlink ref="C15" r:id="rId14" xr:uid="{961A2FDE-E483-449D-8681-8B1B0CEA1956}"/>
+    <hyperlink ref="C16" r:id="rId15" xr:uid="{8B1E63F0-94CA-487D-B60D-9194DB22AF02}"/>
+    <hyperlink ref="C17" r:id="rId16" xr:uid="{834F9FEC-94D5-4ADA-A84D-A85C5CE55BD0}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="0" verticalDpi="0" r:id="rId6"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="0" verticalDpi="0" r:id="rId17"/>
 </worksheet>
 </file>